--- a/光伏配储项目/电价数据/2026/北街站.xlsx
+++ b/光伏配储项目/电价数据/2026/北街站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5295599999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.13324</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.62661</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.92192</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7535599999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6778200000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43938</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45541</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42271</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44507</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.66611</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.54938</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.23467</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.45921</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.48503</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.20495</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.6629400000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.66207</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.63366</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.09705</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.6835800000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.70801</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.48826</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.5573400000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5498099999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.68792</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.6354099999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.66569</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.2378</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.36166</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.50408</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.6028300000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.06714</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.86039</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.72941</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.86121</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.03061</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.85393</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.45678</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.53694</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.22123</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.05205</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.57445</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.1043</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.95929</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.24153</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.05328</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.05805</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.02061</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4222</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.00086</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9180700000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9830599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52251</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53574</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47244</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5385800000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.72038</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72404</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.7524</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.8765700000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.51624</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.6677799999999999</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.73185</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.58701</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.57531</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.45249</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.46834</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.56564</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.9073600000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.93745</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.22199</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.86626</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.06221</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.7710199999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.11949</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.9155</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.76559</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.18019</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.54274</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.43812</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.00396</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.82359</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.77659</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.8124199999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.75301</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.66979</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.25141</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.78122</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.89562</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.94048</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.75291</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16612</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.37642</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.30865</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.29583</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.39391</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.37749</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.54586</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.00815</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.10131</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.59271</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.80899</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.60748</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.58475</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.74176</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3335</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.44293</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52843</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43369</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4441000000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.57372</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.5590700000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.6755399999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5537000000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.64999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.78718</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.09101</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.55196</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8704299999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.12005</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.68332</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.71075</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6122300000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7083200000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8257100000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.80606</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5914299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.45509</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.79614</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.75922</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.83435</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.25953</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.97756</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.0264</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.84321</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.7267100000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.05474</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.12519</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.03524</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.92855</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.9771299999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.9164800000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.32828</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.81311</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.31977</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.8091499999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.83002</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.81608</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.88349</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.81375</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.91195</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.7773099999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.6053500000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.47238</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.80136</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44723</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.5220199999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.50476</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.52338</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.56514</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.76747</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.79826</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.5698799999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.8306399999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.89271</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.53685</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.6290399999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.65421</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.8107300000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.99936</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.74618</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.72414</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.53849</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.44915</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.46251</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.7040299999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.87614</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.6266900000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.66888</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.72854</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.68071</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.65824</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.62219</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.77046</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.50776</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.71585</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.77438</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.7341599999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.54232</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.68451</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.7296</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.67189</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.74837</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.82602</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8335199999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.8323200000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.33788</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.78415</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.74985</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.74626</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.7731699999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.7721</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.70469</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.5334099999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30757</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.49599</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.23902</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.24717</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.16411</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.19369</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.16488</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.22178</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.11935</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.16207</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26774</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.11644</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.11314</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.11385</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.20476</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.22096</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.16833</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.16257</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.16329</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10362</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.11678</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.13931</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.11058</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.23503</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.44039</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.29979</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.70511</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.50354</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.49113</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.19114</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.10982</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.00411</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.17833</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.03584</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.03275</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.02257</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.10876</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.10948</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.10898</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.11726</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.12287</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.12448</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.336</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.36933</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.23163</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.22282</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.53622</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.62899</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.47711</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.57365</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.6944600000000001</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.57759</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.56786</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.65415</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.45659</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14593</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.5325</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.52352</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.49137</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.49836</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47991</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.62276</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79504</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.70577</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.50444</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.9055700000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.17353</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.6761900000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.1885</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.15793</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.57741</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.5924400000000001</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.15488</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.51714</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.14722</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.40691</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.56772</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.25431</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.66818</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80474</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78761</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78851</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88109</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50607</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41653</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46472</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22364</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6392899999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5929800000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.7184199999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56038</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.51695</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.17178</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.80968</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.07048</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.04921</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.02898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.58735</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.6510199999999999</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6079199999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.49476</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.68568</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.58139</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.08319</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.47322</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.54438</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.48575</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.48233</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.47963</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.46033</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.45197</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35313</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95586</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40696</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47911</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5414800000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.51015</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.43851</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.46556</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.5176900000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.59973</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.71482</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.58017</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.6663600000000001</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.5794199999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.64151</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.58708</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.56138</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.65507</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.60584</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.9199700000000001</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6246</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.51051</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.7683300000000001</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.56741</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.9331699999999999</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.53334</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.46485</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.52589</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.92138</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.0247</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.63066</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.30464</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.65167</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.55798</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.38515</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.7503300000000001</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.62962</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.8913300000000001</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.5031100000000001</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.8968400000000001</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.21343</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.87242</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.95201</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.6176900000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.02478</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.9285599999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.70077</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.68738</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.66327</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.7563200000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.04207</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.8585</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.56723</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.8370299999999999</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.51442</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.6930499999999999</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.6653300000000001</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.59153</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.62009</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.60811</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.72151</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.72422</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.7370800000000001</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.94937</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.6909500000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.67816</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.74958</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.64836</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.6636599999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.9262999999999999</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.66988</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.67123</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.73146</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.63293</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.6205499999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.13508</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.78185</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.28799</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.70735</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.6962200000000001</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5861799999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32471</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.72056</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24343</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.67902</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.64137</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.21916</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.25931</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.25136</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.26895</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.25554</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.49536</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54232</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.67159</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.48664</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.68226</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.64693</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.53339</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.49507</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5785399999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6671</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.66274</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.5371900000000001</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.46557</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.50993</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.61433</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.61827</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.60699</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.60939</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.85246</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.8444299999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.55472</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.66512</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.99027</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.59205</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.97446</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.8545</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.84722</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.91461</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6788099999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.02423</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.6605599999999999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.6561900000000001</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.60024</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.84681</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.87664</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.87176</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.84892</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.87337</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.6929299999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.90652</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.06515</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.98786</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.98564</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.9034500000000001</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.91118</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.91926</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.86222</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.9535399999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.59985</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.6474500000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.89727</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.90563</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.89955</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.49861</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.9789500000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.29568</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.92915</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.04311</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.54637</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.47456</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.70961</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.41112</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.94129</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.6291599999999999</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31711</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.64915</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.6014400000000001</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.60592</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.5706599999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.6869299999999999</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.57335</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.50456</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.5039100000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.91127</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5625800000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.5043299999999999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6519400000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83085</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.26813</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.78872</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.12083</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.23905</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.25984</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.62842</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.8297100000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.19727</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.6879500000000001</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.47086</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.68701</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.69824</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.07846</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.64163</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.79757</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.88562</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.11127</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.79969</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.9324</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.79008</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.61551</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8472799999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.4559</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5604600000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.32993</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.46076</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.5317</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.21938</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.19156</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.34348</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.7212</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.71131</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.7259</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.35622</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.3746</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.61299</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.75002</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.57285</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.6425599999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.18173</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.49259</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.42839</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.12501</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.06507</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.9831599999999999</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.96462</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.65761</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.64083</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.9179700000000001</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.5764600000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.77677</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.5460700000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.68074</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.53086</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.70735</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.07709</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.03254</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.82155</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.82269</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.91034</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.94982</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.27364</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.50832</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.35568</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.9985700000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.18219</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.77129</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.62251</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.49001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.83509</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.98958</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.74102</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47813</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47151</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.9897400000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.61502</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.49629</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.43188</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.52422</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.53028</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.78162</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.76489</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.04437</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.10205</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.75278</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.79936</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.8100599999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.43543</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41303</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.48385</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.46488</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.51354</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.5904299999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.7188099999999999</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.13752</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.27296</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2800299999999999</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.21148</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22839</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.13161</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.22754</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.23981</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.16389</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.21812</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25712</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.48604</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.46644</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35168</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.52346</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.18851</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.17886</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.13774</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.12323</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.23083</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.12491</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.13621</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.11865</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.17733</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.20212</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.16492</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.13183</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.12431</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.17246</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.11472</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.13069</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.12033</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.11492</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.13619</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22379</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.11405</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.12047</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.11407</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.20325</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.15358</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.24139</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.5725800000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25472</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7306</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6533</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.46701</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.8100499999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.81304</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.92835</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.77455</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.55924</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.78124</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23227</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.25027</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18304</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.10985</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.12912</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.54553</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.62859</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.10292</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.53842</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.48632</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.78791</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.64149</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.6469600000000001</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.65752</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.76036</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.50395</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.6849500000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.53173</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.61567</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.03225</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.0282</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.06516</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.37228</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.0327</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.10595</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.16044</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.44296</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.79686</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.68448</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.73117</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.72924</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.97135</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8383700000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.66638</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.52803</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33444</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.57116</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.43908</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.53151</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.53213</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22142</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.89323</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.72693</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.6060099999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49259</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.57124</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51205</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.80271</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.71521</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.8055599999999999</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.05524</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.04988</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.7263200000000001</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.74414</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.54388</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.20865</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.4217</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.47777</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.89122</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.56153</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.50658</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.76889</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.73651</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.9116000000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.6184299999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5486599999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.77085</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.65459</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44328</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.43669</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33707</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.49541</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5785399999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.51467</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.72596</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.96282</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.21989</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.44596</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.57384</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.68096</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.71911</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.6667999999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.63971</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.67353</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.65226</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.6412899999999999</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.64447</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.97035</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.6353300000000001</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.65266</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.65771</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.54777</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.63955</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.54587</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.65118</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.6434800000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.65942</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.85526</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.01955</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.06676</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.13343</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.11652</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.1864</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.19885</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.1767</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.87946</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.7760199999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.74609</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.9243400000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.7122200000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.79323</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.68244</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.63276</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.62382</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.60888</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6845800000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.53312</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.5359700000000001</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.5961000000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6398200000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.45336</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.66483</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.5719299999999999</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.66471</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.62875</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.63282</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.54357</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.30523</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.34145</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.71782</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.56002</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.71712</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.64638</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.72519</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.70796</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.70809</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.03539</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.05425</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.6849400000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.25826</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.56267</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.64106</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.62483</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.61936</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.0013</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.00349</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.40736</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.02437</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.41099</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.39262</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.42458</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.12975</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.05432</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.80433</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.7848999999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.45356</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.52703</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.30106</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.30214</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.1245</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.4424</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.53309</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.51047</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.06149</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.90163</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.68432</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.27117</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.24944</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.52607</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.29291</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.29469</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.60688</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.58763</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.5665800000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37506</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.52813</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.50432</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.72645</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.5546</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.7423500000000001</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.7200800000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.90539</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.23521</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.93779</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.87517</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.10634</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.22928</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.12103</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.17971</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.50436</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.60011</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.49365</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.59938</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.45339</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.7284700000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.61614</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.50631</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.62678</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.51524</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.64828</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.73019</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.65151</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.6632400000000001</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.6447200000000001</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.6553300000000001</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.15012</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.23097</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.05502</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.0741</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.22983</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.98888</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.9956499999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.71404</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6944400000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.7429600000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.7384500000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.71989</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.8344600000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.5700599999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37532</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.20084</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.76997</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.8061499999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.00129</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.66237</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.55576</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.46342</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.53669</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.53243</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.52885</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.61856</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.02837</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.61936</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.66085</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.7448899999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.7343099999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.63693</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.84075</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.61741</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.06442</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.5936</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.54749</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6320800000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.52842</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.0552</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.5118199999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.11929</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.70311</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.6532100000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.03064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.15925</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.97846</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.78465</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.75906</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.78798</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.78365</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.8015</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.10133</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.13162</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.20059</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.50138</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.7373999999999999</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.76019</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.7305499999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.78238</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.32036</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.53896</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.8867699999999999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.53452</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.45584</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.8729199999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.57031</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.5724600000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.44187</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.44146</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.42513</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.5818300000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.64463</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.8660399999999999</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.62986</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1.15463</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.51175</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.25837</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.49096</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.52158</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.72703</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.5862999999999999</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.59385</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.6247699999999999</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.65059</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.50218</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.48917</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.57496</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.58533</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.56963</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6038300000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.86803</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.62121</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.54218</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.52747</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.49418</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.49639</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.6210599999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.49979</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
